--- a/sektorler/Otomotiv.xlsx
+++ b/sektorler/Otomotiv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,40 +511,70 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>brüt_kar_marjı_%</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>net_kar_marjı_%</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>aktif_devir_hizi</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ozkaynak_carpani</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>roe_dupont_%</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Piotroski F-Skoru</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Sektör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>F/K (PD)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>FD/FAVÖK (PD)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>FD/NS (PD)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PD/DD (PD)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin PD</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Ortalama Tahmin Fiyat</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>iskonto_%</t>
         </is>
@@ -553,157 +583,193 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67148466000</v>
+        <v>7997260000</v>
       </c>
       <c r="C2" t="n">
-        <v>220000000</v>
+        <v>900000000</v>
       </c>
       <c r="D2" t="n">
-        <v>25184576000</v>
+        <v>8308303000</v>
       </c>
       <c r="E2" t="n">
-        <v>183.1999969482422</v>
+        <v>9.970000267028809</v>
       </c>
       <c r="F2" t="n">
-        <v>40303999328.61328</v>
+        <v>8973000240.325928</v>
       </c>
       <c r="G2" t="n">
-        <v>65488575328.61328</v>
+        <v>17281303240.32593</v>
       </c>
       <c r="H2" t="n">
-        <v>255780842000</v>
+        <v>21051030371</v>
       </c>
       <c r="I2" t="n">
-        <v>11358493000</v>
+        <v>3009021454</v>
       </c>
       <c r="J2" t="n">
-        <v>14717182000</v>
+        <v>3919858843</v>
       </c>
       <c r="K2" t="n">
-        <v>3141080000</v>
+        <v>638762038</v>
       </c>
       <c r="L2" t="n">
-        <v>12.83125527799779</v>
+        <v>14.04748514551819</v>
       </c>
       <c r="M2" t="n">
-        <v>4.449803999747593</v>
+        <v>4.408654477746439</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2560339344281824</v>
+        <v>0.8209243412680043</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6002221901631123</v>
+        <v>1.122009318232235</v>
       </c>
       <c r="P2" t="n">
-        <v>28.18204939760455</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>33.53417333565905</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>29.40476935764334</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.034350465238802</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9104477163145466</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.897998796959029</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8.006062051121352</v>
+      </c>
+      <c r="V2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>42771530349.62836</v>
-      </c>
-      <c r="S2" t="n">
-        <v>125830422701.89</v>
-      </c>
-      <c r="T2" t="n">
-        <v>121665780281.7942</v>
-      </c>
-      <c r="U2" t="n">
-        <v>132731628076.8734</v>
-      </c>
-      <c r="V2" t="n">
-        <v>105749840352.5465</v>
-      </c>
-      <c r="W2" t="n">
-        <v>480.6810925115749</v>
-      </c>
       <c r="X2" t="n">
-        <v>-61.88741354667894</v>
+        <v>8733499474.827236</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>29026228854.81918</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1564982298.40951</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>12569608733.72917</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12973579840.44627</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>14.41508871160697</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-30.83635857890346</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>DOAS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7233449000</v>
+        <v>67808233000</v>
       </c>
       <c r="C3" t="n">
-        <v>900000000</v>
+        <v>220000000</v>
       </c>
       <c r="D3" t="n">
-        <v>7234748000</v>
+        <v>27581721000</v>
       </c>
       <c r="E3" t="n">
-        <v>11.60000038146973</v>
+        <v>187.3999938964844</v>
       </c>
       <c r="F3" t="n">
-        <v>10440000343.32275</v>
+        <v>41227998657.22656</v>
       </c>
       <c r="G3" t="n">
-        <v>17674748343.32275</v>
+        <v>68809719657.22656</v>
       </c>
       <c r="H3" t="n">
-        <v>16599038000</v>
+        <v>276068418325</v>
       </c>
       <c r="I3" t="n">
-        <v>1960380000</v>
+        <v>11836752827</v>
       </c>
       <c r="J3" t="n">
-        <v>2728867000</v>
+        <v>15589790859</v>
       </c>
       <c r="K3" t="n">
-        <v>179091000</v>
+        <v>3275582722</v>
       </c>
       <c r="L3" t="n">
-        <v>58.29438856962524</v>
+        <v>12.5864623660164</v>
       </c>
       <c r="M3" t="n">
-        <v>6.476954847313099</v>
+        <v>4.413767976720653</v>
       </c>
       <c r="N3" t="n">
-        <v>1.064805583511692</v>
+        <v>0.2492487915666641</v>
       </c>
       <c r="O3" t="n">
-        <v>1.443294940397417</v>
+        <v>0.6080087451508516</v>
       </c>
       <c r="P3" t="n">
-        <v>18.77758558938962</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>28.71047155456628</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>11.89343145051324</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.186511206850122</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.917945025804164</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.031633005254868</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4.623312602569056</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>2438650445.65732</v>
-      </c>
-      <c r="S3" t="n">
-        <v>20766526052.5075</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2295186396.865583</v>
-      </c>
-      <c r="U3" t="n">
-        <v>14298278420.55293</v>
-      </c>
-      <c r="V3" t="n">
-        <v>9949660328.895832</v>
-      </c>
-      <c r="W3" t="n">
-        <v>11.05517814321759</v>
-      </c>
       <c r="X3" t="n">
-        <v>4.928208584195337</v>
+        <v>44785535583.65997</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>120902590998.8095</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>101898984123.0295</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>106576872295.7041</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>93540995750.30078</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>425.186344319549</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-55.92520869963693</v>
       </c>
     </row>
     <row r="4">
@@ -713,153 +779,189 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>156020689000</v>
+        <v>164435643000</v>
       </c>
       <c r="C4" t="n">
         <v>3509100000</v>
       </c>
       <c r="D4" t="n">
-        <v>99193516000</v>
+        <v>106438403000</v>
       </c>
       <c r="E4" t="n">
-        <v>102.5999984741211</v>
+        <v>80.55000305175781</v>
       </c>
       <c r="F4" t="n">
-        <v>360033654645.5383</v>
+        <v>282658015708.9233</v>
       </c>
       <c r="G4" t="n">
-        <v>459227170645.5383</v>
+        <v>389096418708.9233</v>
       </c>
       <c r="H4" t="n">
-        <v>830827933000</v>
+        <v>896123726762</v>
       </c>
       <c r="I4" t="n">
-        <v>34899678000</v>
+        <v>34302121450</v>
       </c>
       <c r="J4" t="n">
-        <v>52105072000</v>
+        <v>53771966985</v>
       </c>
       <c r="K4" t="n">
-        <v>33986135000</v>
+        <v>34407880194</v>
       </c>
       <c r="L4" t="n">
-        <v>10.59354512201927</v>
+        <v>8.214920945877184</v>
       </c>
       <c r="M4" t="n">
-        <v>8.813483083672514</v>
+        <v>7.23604585298998</v>
       </c>
       <c r="N4" t="n">
-        <v>0.552734389884239</v>
+        <v>0.4341994381901494</v>
       </c>
       <c r="O4" t="n">
-        <v>2.307602004279947</v>
+        <v>1.718958314341395</v>
       </c>
       <c r="P4" t="n">
-        <v>9.693448806712128</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>12.13555588153699</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.973186515457166</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.839634993074827</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.877450272809465</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.840101029249143</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20.47350378522265</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>462783184324.8395</v>
-      </c>
-      <c r="S4" t="n">
-        <v>435463688106.1857</v>
-      </c>
-      <c r="T4" t="n">
-        <v>377806156907.1548</v>
-      </c>
-      <c r="U4" t="n">
-        <v>308404365702.7927</v>
-      </c>
-      <c r="V4" t="n">
-        <v>396114348760.2432</v>
-      </c>
-      <c r="W4" t="n">
-        <v>112.8820349264037</v>
-      </c>
       <c r="X4" t="n">
-        <v>-9.108656181637953</v>
+        <v>470443116101.739</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>405710451003.4572</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>313858611495.9655</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>258449980917.1107</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>362115539879.5681</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>103.1932802939694</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-21.94258887565848</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>TTRAK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16714729077</v>
+        <v>65740826000</v>
       </c>
       <c r="C5" t="n">
-        <v>100066875</v>
+        <v>500000000</v>
       </c>
       <c r="D5" t="n">
-        <v>8743941158</v>
+        <v>59134215000</v>
       </c>
       <c r="E5" t="n">
-        <v>470.25</v>
+        <v>273.5</v>
       </c>
       <c r="F5" t="n">
-        <v>47056447968.75</v>
+        <v>136750000000</v>
       </c>
       <c r="G5" t="n">
-        <v>55800389126.75</v>
+        <v>195884215000</v>
       </c>
       <c r="H5" t="n">
-        <v>53837290099</v>
+        <v>452300219732</v>
       </c>
       <c r="I5" t="n">
-        <v>2080768598</v>
+        <v>5311539630</v>
       </c>
       <c r="J5" t="n">
-        <v>4955717834</v>
+        <v>12430594979</v>
       </c>
       <c r="K5" t="n">
-        <v>454804634</v>
+        <v>14011380783</v>
       </c>
       <c r="L5" t="n">
-        <v>103.4651902178068</v>
+        <v>9.759923173733076</v>
       </c>
       <c r="M5" t="n">
-        <v>11.25979948735515</v>
+        <v>15.7582332407196</v>
       </c>
       <c r="N5" t="n">
-        <v>1.03646355572764</v>
+        <v>0.4330845010777723</v>
       </c>
       <c r="O5" t="n">
-        <v>2.815268363128971</v>
+        <v>2.08013814733633</v>
       </c>
       <c r="P5" t="n">
-        <v>4.421856489001954</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+        <v>3.884124043875686</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>6.580660538842137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.097805433590573</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.171231643690298</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.340909325826009</v>
+      </c>
+      <c r="U5" t="n">
+        <v>22.47113380644815</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>6192994195.080234</v>
-      </c>
-      <c r="S5" t="n">
-        <v>42107351043.7573</v>
-      </c>
-      <c r="T5" t="n">
-        <v>22165430984.43928</v>
-      </c>
-      <c r="U5" t="n">
-        <v>33039819602.93875</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25876398956.55389</v>
-      </c>
-      <c r="W5" t="n">
-        <v>258.5910567963064</v>
-      </c>
       <c r="X5" t="n">
-        <v>81.85083653933887</v>
+        <v>191571163328.7996</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>59260467769.40472</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>153002152258.265</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>103327447232.1983</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>126790307647.1669</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>253.5806152943338</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>7.855247406252075</v>
       </c>
     </row>
     <row r="6">
@@ -869,154 +971,180 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14512045827</v>
+        <v>15862084113</v>
       </c>
       <c r="C6" t="n">
         <v>252000000</v>
       </c>
       <c r="D6" t="n">
-        <v>6284158313</v>
+        <v>9870066958</v>
       </c>
       <c r="E6" t="n">
-        <v>70.25</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="F6" t="n">
-        <v>17703000000</v>
+        <v>12826800384.52148</v>
       </c>
       <c r="G6" t="n">
-        <v>23987158313</v>
+        <v>22696867342.52148</v>
       </c>
       <c r="H6" t="n">
-        <v>26686841318</v>
+        <v>31100299355</v>
       </c>
       <c r="I6" t="n">
-        <v>595032161</v>
+        <v>387583241</v>
       </c>
       <c r="J6" t="n">
-        <v>1513463117</v>
+        <v>1428248217</v>
       </c>
       <c r="K6" t="n">
-        <v>904947192</v>
+        <v>407270800</v>
       </c>
       <c r="L6" t="n">
-        <v>19.56246746384733</v>
+        <v>31.494524980729</v>
       </c>
       <c r="M6" t="n">
-        <v>15.84918591247044</v>
+        <v>15.89140253939591</v>
       </c>
       <c r="N6" t="n">
-        <v>0.898838421046889</v>
+        <v>0.72979578374613</v>
       </c>
       <c r="O6" t="n">
-        <v>1.219883137845607</v>
+        <v>0.8086453389822271</v>
       </c>
       <c r="P6" t="n">
-        <v>3.361193927582896</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>3.021667363497051</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13.90688816409947</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.309539806518046</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.666414437572615</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.932227419211738</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.558943824921066</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>12322505726.51412</v>
-      </c>
-      <c r="S6" t="n">
-        <v>9245691807.023884</v>
-      </c>
-      <c r="T6" t="n">
-        <v>9037443277.411554</v>
-      </c>
-      <c r="U6" t="n">
-        <v>28685800050.05486</v>
-      </c>
-      <c r="V6" t="n">
-        <v>14822860215.2511</v>
-      </c>
-      <c r="W6" t="n">
-        <v>58.82087387004406</v>
-      </c>
       <c r="X6" t="n">
-        <v>19.43039159058888</v>
+        <v>5568426278.194804</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3733223540.431652</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4716493556.437647</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>24931062764.2357</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>9737301534.824951</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>38.64008545565457</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>31.72849108808125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TMSN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60031247000</v>
+        <v>15443065482</v>
       </c>
       <c r="C7" t="n">
-        <v>500000000</v>
+        <v>115000000</v>
       </c>
       <c r="D7" t="n">
-        <v>33530388000</v>
+        <v>6660840032</v>
       </c>
       <c r="E7" t="n">
-        <v>297</v>
+        <v>81.55000305175781</v>
       </c>
       <c r="F7" t="n">
-        <v>148500000000</v>
+        <v>9378250350.952148</v>
       </c>
       <c r="G7" t="n">
-        <v>182030388000</v>
+        <v>16039090382.95215</v>
       </c>
       <c r="H7" t="n">
-        <v>319413508000</v>
+        <v>2164804765</v>
       </c>
       <c r="I7" t="n">
-        <v>2516656000</v>
+        <v>-1721626963</v>
       </c>
       <c r="J7" t="n">
-        <v>9997606000</v>
+        <v>-1089321011</v>
       </c>
       <c r="K7" t="n">
-        <v>8353933000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.77605829493725</v>
-      </c>
-      <c r="M7" t="n">
-        <v>18.20739765099765</v>
-      </c>
+        <v>-4134559158</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0.5698894487580657</v>
+        <v>7.409023964778712</v>
       </c>
       <c r="O7" t="n">
-        <v>2.473711732158421</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.694717845117845</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>0.607279063983972</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>-13.17143955011574</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-190.9899324339301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.07845834542754501</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.738046751668022</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-26.04420317429204</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>113754026910.5728</v>
-      </c>
-      <c r="S7" t="n">
-        <v>69056401856.37381</v>
-      </c>
-      <c r="T7" t="n">
-        <v>149853117520.7838</v>
-      </c>
-      <c r="U7" t="n">
-        <v>118663100208.3491</v>
-      </c>
-      <c r="V7" t="n">
-        <v>112831661624.0199</v>
-      </c>
-      <c r="W7" t="n">
-        <v>225.6633232480397</v>
-      </c>
       <c r="X7" t="n">
-        <v>31.61199424221453</v>
-      </c>
+        <v>-56529925209.8559</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-17036032510.66022</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-5645510393.33082</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>24272474667.3359</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-13734748361.62776</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1025,143 +1153,175 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8548807000</v>
+        <v>5508500000</v>
       </c>
       <c r="C8" t="n">
         <v>120000000</v>
       </c>
       <c r="D8" t="n">
-        <v>27820647000</v>
+        <v>42900883000</v>
       </c>
       <c r="E8" t="n">
-        <v>383</v>
+        <v>299.75</v>
       </c>
       <c r="F8" t="n">
-        <v>45960000000</v>
+        <v>35970000000</v>
       </c>
       <c r="G8" t="n">
-        <v>73780647000</v>
+        <v>78870883000</v>
       </c>
       <c r="H8" t="n">
-        <v>51962379000</v>
+        <v>56151855094</v>
       </c>
       <c r="I8" t="n">
-        <v>126584000</v>
+        <v>-4119056617</v>
       </c>
       <c r="J8" t="n">
-        <v>2153293000</v>
+        <v>-1436508084</v>
       </c>
       <c r="K8" t="n">
-        <v>-1458959000</v>
+        <v>-6106814813</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>34.26410014800587</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>1.419885856265357</v>
+        <v>1.40459977445033</v>
       </c>
       <c r="O8" t="n">
-        <v>5.37618874773989</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.2754221061792863</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>6.529908323500045</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>13.87584548712897</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-10.87553528334371</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7638334263154748</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11.02729101210151</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-91.6047802584887</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>-19866386449.0441</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-5725415752.619305</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2012290485.598011</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16898331992.05135</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1670294931.003512</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>-83495669418.91853</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-56582844256.73683</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-16564723885.34878</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8657926553.56299</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-36996327751.86029</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>TMSN</t>
+          <t>TTRAK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14819366913</v>
+        <v>18976413610</v>
       </c>
       <c r="C9" t="n">
-        <v>115000000</v>
+        <v>100066875</v>
       </c>
       <c r="D9" t="n">
-        <v>4803971802</v>
+        <v>8965040226</v>
       </c>
       <c r="E9" t="n">
-        <v>104.5</v>
+        <v>408</v>
       </c>
       <c r="F9" t="n">
-        <v>12017500000</v>
+        <v>40827285000</v>
       </c>
       <c r="G9" t="n">
-        <v>16821471802</v>
+        <v>49792325226</v>
       </c>
       <c r="H9" t="n">
-        <v>3454240450</v>
+        <v>52760167934</v>
       </c>
       <c r="I9" t="n">
-        <v>-1541465006</v>
+        <v>-221128665</v>
       </c>
       <c r="J9" t="n">
-        <v>-967348275</v>
+        <v>3418809170</v>
       </c>
       <c r="K9" t="n">
-        <v>4525144877</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.655716076866725</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>-911666439</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>14.56423062829213</v>
+      </c>
       <c r="N9" t="n">
-        <v>4.869803375152995</v>
+        <v>0.9437484218831032</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8109320776353734</v>
+        <v>2.151475291331406</v>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>10.92026049691004</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1.727944536000043</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.229900137005294</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.378757201071919</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-5.05533295200781</v>
+      </c>
+      <c r="V9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Otomotiv</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>61618096782.97618</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-14730063528.89449</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-2820803567.822848</v>
-      </c>
-      <c r="U9" t="n">
-        <v>29293278232.6113</v>
-      </c>
-      <c r="V9" t="n">
-        <v>18340126979.71754</v>
-      </c>
-      <c r="W9" t="n">
-        <v>159.479365041022</v>
-      </c>
       <c r="X9" t="n">
-        <v>-34.47428137607645</v>
+        <v>-12464795796.49678</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>23597264942.42438</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15780360888.52196</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>29825977178.07264</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>14184701803.13055</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>141.7522212333557</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>187.8261775724426</v>
       </c>
     </row>
     <row r="10">
@@ -1171,60 +1331,66 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>345028799817</v>
+        <v>361772025205</v>
       </c>
       <c r="C10" t="n">
         <v>5716166875</v>
       </c>
       <c r="D10" t="n">
-        <v>212795946273</v>
+        <v>269859472216</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>682014602286.2244</v>
+        <v>568611350341.9495</v>
       </c>
       <c r="G10" t="n">
-        <v>894810548559.2244</v>
+        <v>838470822557.9495</v>
       </c>
       <c r="H10" t="n">
-        <v>1558562071867</v>
+        <v>1787720522338</v>
       </c>
       <c r="I10" t="n">
-        <v>51996126753</v>
+        <v>48785206357</v>
       </c>
       <c r="J10" t="n">
-        <v>87203852676</v>
+        <v>88033439958</v>
       </c>
       <c r="K10" t="n">
-        <v>50086176703</v>
+        <v>41587836127</v>
       </c>
       <c r="L10" t="n">
-        <v>13.61682298751651</v>
+        <v>13.67253993705123</v>
       </c>
       <c r="M10" t="n">
-        <v>10.26113550147643</v>
+        <v>9.524458239482369</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5741257051683105</v>
+        <v>0.4690167238564719</v>
       </c>
       <c r="O10" t="n">
-        <v>1.976688910166219</v>
+        <v>1.571739412464916</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0762390227110981</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Otomotiv</t>
-        </is>
-      </c>
+        <v>0.08579710258625989</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Otomotiv</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1233,60 +1399,66 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15767047995</v>
+        <v>17419248861.5</v>
       </c>
       <c r="C11" t="n">
         <v>236000000</v>
       </c>
       <c r="D11" t="n">
-        <v>16964258579</v>
+        <v>18725893979</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>43131999664.30664</v>
+        <v>38398642500</v>
       </c>
       <c r="G11" t="n">
-        <v>60644482227.68164</v>
+        <v>59301022441.61328</v>
       </c>
       <c r="H11" t="n">
-        <v>52899834549.5</v>
+        <v>54456011514</v>
       </c>
       <c r="I11" t="n">
-        <v>2020574299</v>
+        <v>1698302347.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3842292417</v>
+        <v>3669334006.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2023013596</v>
+        <v>523016419</v>
       </c>
       <c r="L11" t="n">
-        <v>17.77605829493725</v>
+        <v>12.5864623660164</v>
       </c>
       <c r="M11" t="n">
-        <v>11.25979948735515</v>
+        <v>10.90013824064106</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9676509883872644</v>
+        <v>0.7753600625070671</v>
       </c>
       <c r="O11" t="n">
-        <v>1.875448472338682</v>
+        <v>1.420483816286815</v>
       </c>
       <c r="P11" t="n">
-        <v>4.421856489001954</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Otomotiv</t>
-        </is>
-      </c>
+        <v>12.13555588153699</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Otomotiv</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
